--- a/lab03/dados/rotulagem/avaliador_2.xlsx
+++ b/lab03/dados/rotulagem/avaliador_2.xlsx
@@ -476,6 +476,16 @@
           <t>https://github.com/tldraw/tldraw</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -488,6 +498,21 @@
           <t>https://github.com/babel/babel</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>README não diz como o projeto é usado; pesou o fato de @babel/core, plugins e presets serem consumidos como dependência (a CLI existe, mas é secundária)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -500,6 +525,16 @@
           <t>https://github.com/tw93/Pake</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -512,6 +547,16 @@
           <t>https://github.com/firecrawl/firecrawl</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -524,6 +569,21 @@
           <t>https://github.com/sickn33/agentic-awesome-skills</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>o conteúdo central é um acervo de arquivos SKILL.md; a CLI e o servidor MCP só dão acesso a esse acervo. Há release quase todo dia, mas com notas detalhadas e pacote no npm</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -536,6 +596,16 @@
           <t>https://github.com/gogs/gogs</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -548,6 +618,21 @@
           <t>https://github.com/prettier/prettier</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>README mostra rodar no editor, em hook de pré-commit e no CI, com CLI e API na documentação; tratei a CLI como modo principal</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -560,6 +645,21 @@
           <t>https://github.com/headroomlabs-ai/headroom</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>o README lista primeiro o uso como biblioteca (compress), e só depois proxy, wrap de agentes e MCP</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -572,6 +672,16 @@
           <t>https://github.com/anomalyco/opencode</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -584,6 +694,16 @@
           <t>https://github.com/jamiepine/voicebox</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -596,6 +716,16 @@
           <t>https://github.com/serverless/serverless</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -608,6 +738,21 @@
           <t>https://github.com/paperclipai/paperclip</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>servidor/aplicação que o usuário sobe e opera; releases com notas e assets</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -620,6 +765,21 @@
           <t>https://github.com/JuliaLang/julia</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>repositório de uma linguagem; quem usa roda o executável julia (REPL ou scripts)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -632,6 +792,16 @@
           <t>https://github.com/axios/axios</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -644,6 +814,21 @@
           <t>https://github.com/debpalash/VoiceStudio</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>releases frequentes, mas com instaladores (assets) e notas detalhadas na maioria</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -656,6 +841,21 @@
           <t>https://github.com/HKUDS/nanobot</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>autodescrito como "framework", mas o README apresenta uso como agente auto-hospedado (WebUI, chat apps, docker); tipo decidido pelo modo de uso apresentado</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -668,6 +868,16 @@
           <t>https://github.com/facebookresearch/faiss</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -680,6 +890,21 @@
           <t>https://github.com/Homebrew/brew</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>releases quase semanais com notas geradas automaticamente, descrevendo os PRs</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -692,6 +917,16 @@
           <t>https://github.com/coollabsio/coolify</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -704,6 +939,21 @@
           <t>https://github.com/heygen-com/hyperframes</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>README apresenta o framework antes da CLI e dos plugins de agentes. Várias releases por dia, automáticas, mas com notas e pacote npm</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -716,6 +966,16 @@
           <t>https://github.com/OpenHands/OpenHands</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -728,6 +988,21 @@
           <t>https://github.com/toeverything/AFFiNE</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>as 30 mais recentes são quase todas canary diárias (marcadores automáticos), mas as estáveis, que foram as sorteadas, trazem notas e instaladores</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -740,6 +1015,21 @@
           <t>https://github.com/jestjs/jest</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>framework de testes; README mostra instalação como dependência e uso por CLI</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -752,6 +1042,21 @@
           <t>https://github.com/getsentry/sentry</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>plataforma de monitoramento hospedada/auto-hospedada; releases mensais com notas e assets</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -764,6 +1069,21 @@
           <t>https://github.com/redis/redis</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>servidor iniciado por comando</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -776,6 +1096,21 @@
           <t>https://github.com/supabase/supabase</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>incerto</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>releases são resumos mensais ("tudo que aconteceu no mês") de uma plataforma hospedada, sem artefato; não está claro que a tag corresponda a uma versão distribuída ao usuário</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -788,6 +1123,21 @@
           <t>https://github.com/exelban/stats</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>app de barra de menu do macOS</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -800,6 +1150,21 @@
           <t>https://github.com/llvm/llvm-project</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>conjunto de componentes reutilizáveis de compilador e toolchain (toolkit, bibliotecas, headers), embora também entregue ferramentas de terminal</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -812,6 +1177,21 @@
           <t>https://github.com/makeplane/plane</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>a página mistura rc pré-release com releases estáveis; as estáveis têm notas e artefatos</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -824,6 +1204,21 @@
           <t>https://github.com/microsoft/monaco-editor</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>pacote npm; notas listam os PRs gerados automaticamente</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -836,6 +1231,21 @@
           <t>https://github.com/langchain-ai/langchain</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>monorepo; README apresenta o pacote langchain como principal; releases são tags por pacote (pacote==versão), publicadas no PyPI</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -848,6 +1258,16 @@
           <t>https://github.com/crewAIInc/crewAI</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -860,6 +1280,21 @@
           <t>https://github.com/rust-lang/rust</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>repositório da linguagem (compilador, biblioteca padrão, docs); o uso típico é chamar rustc/cargo no terminal</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -872,6 +1307,21 @@
           <t>https://github.com/ggml-org/llama.cpp</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>README trata a biblioteca llama como produto principal e os binários como forma de uso; tags bNNNN saem por commit, porém com binários e mensagem do commit anexos</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -884,6 +1334,21 @@
           <t>https://github.com/metabase/metabase</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>notas das releases são padrão (instruções de upgrade, imagem Docker e JAR), sem lista de mudanças; mudanças identificadas pelos commits</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -896,6 +1361,21 @@
           <t>https://github.com/cline/cline</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>monorepo com CLI, app desktop, extensões e SDK; o README abre pela CLI, então foi o modo adotado. Tags separadas por componente</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -908,6 +1388,21 @@
           <t>https://github.com/yt-dlp/yt-dlp</t>
         </is>
       </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>README abre como "command-line audio/video downloader"; uso é yt-dlp [OPTIONS] URL</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -920,6 +1415,21 @@
           <t>https://github.com/rtk-ai/rtk</t>
         </is>
       </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>builds dev (pré-release) ignorados; releases estáveis têm notas e binários</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -932,6 +1442,21 @@
           <t>https://github.com/denoland/deno</t>
         </is>
       </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>runtime de JS/TS usado via comando deno (run, test, task etc.), distribuído como binário</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -944,6 +1469,21 @@
           <t>https://github.com/modelcontextprotocol/servers</t>
         </is>
       </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>monorepo de servidores de referência (exemplos educacionais) sem pacote principal; releases por data publicam pacotes npm/PyPI</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -956,6 +1496,21 @@
           <t>https://github.com/opendatalab/MinerU</t>
         </is>
       </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>README orienta o uso por linha de comando (mineru parse/read), com SDK e WebUI como secundários</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -968,6 +1523,21 @@
           <t>https://github.com/astral-sh/uv</t>
         </is>
       </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>gerenciador de pacotes Python usado pelo comando uv</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -980,6 +1550,21 @@
           <t>https://github.com/tinyhumansai/openhuman</t>
         </is>
       </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>README apresenta app desktop (UI-first, instaladores) como modo principal; CLI/TUI/embed são secundários</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -992,6 +1577,21 @@
           <t>https://github.com/microsoft/playwright</t>
         </is>
       </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>biblioteca/framework de automação e testes consumida como API (@playwright/test, pacotes por linguagem); CLI é acessória</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1004,6 +1604,21 @@
           <t>https://github.com/bitcoin/bitcoin</t>
         </is>
       </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>README descreve nó completo que valida blocos (bitcoind/bitcoin-qt), com carteira e GUI opcionais; binários assinados no bitcoincore.org</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1016,6 +1631,21 @@
           <t>https://github.com/puppeteer/puppeteer</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>README apresenta biblioteca JS com API de alto nível para controlar Chrome/Firefox; pacotes puppeteer/puppeteer-core no npm</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1028,6 +1658,21 @@
           <t>https://github.com/vectorize-io/hindsight</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>README apresenta sistema de memória para agentes que se sobe como servidor/API (Docker, pip, Helm); SDKs e CLI são clientes</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1040,6 +1685,21 @@
           <t>https://github.com/abhigyanpatwari/GitNexus</t>
         </is>
       </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>README recomenda CLI + servidor MCP (npx gitnexus analyze/setup); a Web UI é secundária</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1052,6 +1712,21 @@
           <t>https://github.com/openbq-org/OpenBB</t>
         </is>
       </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>incerto</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>README apresenta o pacote Python openbb (pip) como uso principal, com CLI/API como extras. As tags misturam pacote (v4.5.0, openbb-v5.0.0), app desktop (Open Data Platform-v1.0.x) e a tag móvel "ODP" (ponteiro para a versão estável), então não há um único artefato entregue</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1064,6 +1739,21 @@
           <t>https://github.com/MHSanaei/3x-ui</t>
         </is>
       </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>painel web de administração do Xray-core instalado em servidor (x-ui); API REST e menu x-ui no terminal são complementos</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1076,6 +1766,21 @@
           <t>https://github.com/TryGhost/Ghost</t>
         </is>
       </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>plataforma de publicação/CMS que se hospeda ou instala como serviço</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1088,6 +1793,21 @@
           <t>https://github.com/usememos/memos</t>
         </is>
       </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>README: app de notas rápidas auto-hospedado (servidor + web)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1100,6 +1820,21 @@
           <t>https://github.com/jgm/pandoc</t>
         </is>
       </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>README: conversor de documentos usado como comando pandoc (a biblioteca Haskell é secundária)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1112,6 +1847,21 @@
           <t>https://github.com/mermaid-js/mermaid</t>
         </is>
       </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>README: biblioteca JavaScript (npm/CDN) que renderiza diagramas a partir de texto</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1124,6 +1874,21 @@
           <t>https://github.com/outline/outline</t>
         </is>
       </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>README: base de conhecimento colaborativa (React/Node) que se hospeda ou usa pelo serviço do projeto; o repositório é o código do serviço</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1136,6 +1901,21 @@
           <t>https://github.com/agno-agi/agno</t>
         </is>
       </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>README: framework/SDK para construir plataformas de agentes (AgentOS é o runtime e a UI sobre o SDK); usado como biblioteca Python</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1148,6 +1928,21 @@
           <t>https://github.com/coder/code-server</t>
         </is>
       </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>VS Code servido no navegador, instalado em servidor Linux (código remoto); usuário acessa por URL</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1160,6 +1955,21 @@
           <t>https://github.com/spring-projects/spring-boot</t>
         </is>
       </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>framework Java (README: aplicações Spring prontas para produção; tag "framework") usado como dependência/starters</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1172,6 +1982,21 @@
           <t>https://github.com/ionic-team/ionic-framework</t>
         </is>
       </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>toolkit de componentes web (Web Components) para Angular/React/Vue consumido como pacote npm</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1182,6 +2007,21 @@
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>https://github.com/harry0703/MoneyPrinterTurbo</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ferramenta que gera vídeos curtos com IA, usada por WebUI/API (também CLI e agente); projeto rodado localmente ou em Docker</t>
         </is>
       </c>
     </row>
@@ -1330,6 +2170,16 @@
           <t>https://github.com/tldraw/tldraw/compare/v3.15.6...v4.3.2</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>só há seção Bug Fixes (crash); o compare parte de v3.15.6 (918 commits), então decidi pelas notas</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1352,6 +2202,11 @@
           <t>https://github.com/tldraw/tldraw/compare/v4.5.8...v4.5.9</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1374,6 +2229,11 @@
           <t>https://github.com/tldraw/tldraw/compare/v5.2.1...v5.2.2</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1396,6 +2256,16 @@
           <t>https://github.com/tldraw/tldraw/compare/v5.2.4...v5.2.5</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>notas vazias e commits apenas de docs e bump de versão</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1418,6 +2288,16 @@
           <t>https://github.com/tldraw/tldraw/compare/v5.3.1...v5.3.2</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hotfix com seção Bug Fixes; os itens de metadata são internos, não funcionalidade anunciada</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1440,6 +2320,11 @@
           <t>https://github.com/babel/babel/compare/v7.28.4...v7.28.5</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1462,6 +2347,11 @@
           <t>https://github.com/babel/babel/compare/v7.28.5...v7.28.6</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1484,6 +2374,16 @@
           <t>https://github.com/babel/babel/compare/v7.29.2...v7.29.3</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>combina bug fix, spec compliance (flow), polish e performance; as correções não predominam com clareza</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1506,6 +2406,11 @@
           <t>https://github.com/babel/babel/compare/v7.29.5...v7.29.6</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1528,6 +2433,11 @@
           <t>https://github.com/babel/babel/compare/v8.0.0...v8.0.1</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1550,6 +2460,11 @@
           <t>https://github.com/tw93/Pake/compare/V3.3.5...V3.4.0</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1572,6 +2487,16 @@
           <t>https://github.com/tw93/Pake/compare/V3.4.0...V3.4.3</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>notas repetem o changelog da 3.4.0 com funcionalidades novas e o compare inclui commit que adiciona --maximize/--start-to-tray, além das correções</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1594,6 +2519,11 @@
           <t>https://github.com/tw93/Pake/compare/V3.10.0...V3.11.0</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1616,6 +2546,11 @@
           <t>https://github.com/tw93/Pake/compare/V3.13.1...V3.14.0</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1638,6 +2573,16 @@
           <t>https://github.com/tw93/Pake/compare/V3.15.1...V3.15.6</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>correções predominam, mas as notas anunciam Node mínimo 20 (quebra de compatibilidade); caso de fronteira</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1660,6 +2605,11 @@
           <t>https://github.com/firecrawl/firecrawl/compare/v2.3.0...v2.4.0</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1682,6 +2632,11 @@
           <t>https://github.com/firecrawl/firecrawl/compare/v2.4.0...v2.5.0</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1704,6 +2659,11 @@
           <t>https://github.com/firecrawl/firecrawl/compare/v2.5.0...v2.6.0</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1726,6 +2686,11 @@
           <t>https://github.com/firecrawl/firecrawl/compare/v2.8.0...v2.9.0</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1748,6 +2713,11 @@
           <t>https://github.com/firecrawl/firecrawl/compare/v2.10...v2.11.0</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1770,6 +2740,11 @@
           <t>https://github.com/sickn33/agentic-awesome-skills/compare/v2.9.0...v2.10.0</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1792,6 +2767,11 @@
           <t>https://github.com/sickn33/agentic-awesome-skills/compare/v13.7.0...v13.8.0</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1814,6 +2794,11 @@
           <t>https://github.com/sickn33/agentic-awesome-skills/compare/v13.11.0...v13.12.0</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1836,6 +2821,11 @@
           <t>https://github.com/sickn33/agentic-awesome-skills/compare/v15.4.0...v15.5.0</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1858,6 +2848,11 @@
           <t>https://github.com/sickn33/agentic-awesome-skills/compare/v18.3.0...v18.4.0</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1880,6 +2875,11 @@
           <t>https://github.com/gogs/gogs/compare/v0.13.3...v0.13.4</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1902,6 +2902,16 @@
           <t>https://github.com/gogs/gogs/compare/v0.13.4...v0.14.0</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>release retirada (pulled back); notas não descrevem correção; 308 commits com bumps de dependência e mudanças</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1924,6 +2934,16 @@
           <t>https://github.com/gogs/gogs/compare/v0.14.0...v0.14.1</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>notas listam funcionalidades novas (Added)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1946,6 +2966,11 @@
           <t>https://github.com/gogs/gogs/compare/v0.14.1...v0.14.2</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1968,6 +2993,11 @@
           <t>https://github.com/gogs/gogs/compare/v0.14.2...v0.14.3</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1990,6 +3020,16 @@
           <t>https://github.com/prettier/prettier/compare/3.6.2...3.7.0</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>notas só com link para o blog; compare de 461 commits sem isolar correções</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2012,6 +3052,11 @@
           <t>https://github.com/prettier/prettier/compare/3.7.0...3.7.1</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2034,6 +3079,11 @@
           <t>https://github.com/prettier/prettier/compare/3.8.2...3.8.3</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2056,6 +3106,16 @@
           <t>https://github.com/prettier/prettier/compare/3.9.4...3.9.5</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>notas só com link; commits são majoritariamente testes e dependências, com itens de formatação novos (decorators com declare, Less :extend)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2078,6 +3138,16 @@
           <t>https://github.com/prettier/prettier/compare/3.9.6...3.9.7</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>muitas correções de Markdown, mas as notas anunciam suporte ao Angular 22.2 (e @boundary/@error)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2100,6 +3170,11 @@
           <t>https://github.com/headroomlabs-ai/headroom/compare/v0.13.4...v0.13.5</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2122,6 +3197,11 @@
           <t>https://github.com/headroomlabs-ai/headroom/compare/v0.18.1...v0.18.2</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2144,6 +3224,16 @@
           <t>https://github.com/headroomlabs-ai/headroom/compare/v0.21.31...v0.21.32</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>rotulada "Bug Fixes", mas o conteúdo estende a política com novos campos de ajuste, sem defeito descrito</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2166,6 +3256,11 @@
           <t>https://github.com/headroomlabs-ai/headroom/compare/v0.25.0...v0.26.0</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2188,6 +3283,11 @@
           <t>https://github.com/headroomlabs-ai/headroom/compare/v0.29.0...v0.30.0</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2210,6 +3310,11 @@
           <t>https://github.com/anomalyco/opencode/compare/v0.15.24...v0.15.26</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2232,6 +3337,11 @@
           <t>https://github.com/anomalyco/opencode/compare/v1.0.16...v1.0.17</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2254,6 +3364,11 @@
           <t>https://github.com/anomalyco/opencode/compare/v1.0.24...v1.0.25</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2276,6 +3391,11 @@
           <t>https://github.com/anomalyco/opencode/compare/v1.0.33...v1.0.34</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2298,6 +3418,16 @@
           <t>https://github.com/anomalyco/opencode/compare/v1.1.57...v1.1.58</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>muitas correções, mas anuncia placeholder novo no prompt (funcionalidade nova)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2315,6 +3445,16 @@
           <t>https://github.com/jamiepine/voicebox/releases/tag/v0.1.1</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>primeira release do repositório, sem anterior; notas anunciam funcionalidades</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2337,6 +3477,16 @@
           <t>https://github.com/jamiepine/voicebox/compare/v0.1.7...v0.1.8</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>seção de correções, mas anuncia funcionalidades (endpoint /shutdown, gpu_type)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2359,6 +3509,11 @@
           <t>https://github.com/jamiepine/voicebox/compare/v0.1.10...v0.1.11</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2381,6 +3536,11 @@
           <t>https://github.com/jamiepine/voicebox/compare/v0.2.2...v0.2.3</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2403,6 +3563,11 @@
           <t>https://github.com/jamiepine/voicebox/compare/v0.4.4...v0.4.5</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2425,6 +3590,16 @@
           <t>https://github.com/serverless/serverless/compare/v4.21.0...v4.21.1</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>compare sem commits listados; decidido pelas notas</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2447,6 +3622,16 @@
           <t>https://github.com/serverless/serverless/compare/v4.29.0...sf-core@4.29.3</t>
         </is>
       </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>correção de validação de entrada na ferramenta MCP; resto é manutenção de dependências</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2469,6 +3654,11 @@
           <t>https://github.com/serverless/serverless/compare/sf-core@4.29.3...sf-core@4.29.4</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2491,6 +3681,11 @@
           <t>https://github.com/serverless/serverless/compare/sf-core@4.31.0...sf-core@4.31.1</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2513,6 +3708,11 @@
           <t>https://github.com/serverless/serverless/compare/sf-core@4.33.3...sf-core@4.34.0</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2530,6 +3730,16 @@
           <t>https://github.com/paperclipai/paperclip/releases/tag/v0.3.0</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>notas dominadas por funcionalidades novas</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2552,6 +3762,16 @@
           <t>https://github.com/paperclipai/paperclip/compare/v2026.428.0...v2026.512.0</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Highlights listam planning mode, busca global, adapters novos; correções são poucas e secundárias</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2574,6 +3794,16 @@
           <t>https://github.com/paperclipai/paperclip/compare/v2026.517.0...v2026.525.0</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>notas dominadas por funcionalidades novas</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2596,6 +3826,16 @@
           <t>https://github.com/paperclipai/paperclip/compare/v2026.626.0...v2026.707.0</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>notas dominadas por funcionalidades novas</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2618,6 +3858,16 @@
           <t>https://github.com/paperclipai/paperclip/compare/v2026.831.1...v2026.916.0</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>notas dominadas por funcionalidades novas</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2640,6 +3890,11 @@
           <t>https://github.com/JuliaLang/julia/compare/v1.11.7...v1.12.0</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2662,6 +3917,16 @@
           <t>https://github.com/JuliaLang/julia/compare/v1.12.3...v1.12.4</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>notas só trazem link; commits do backport são correções reais (buffer overflow, world age, rpath do 7z) mais bumps de stdlib e limpeza de warnings</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2684,6 +3949,16 @@
           <t>https://github.com/JuliaLang/julia/compare/v1.10.11...v1.12.6</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>notas só com link; compare listado é v1.10.11...v1.12.6 (4321 commits entre minors), não isola a release; sem evidência legível</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2706,6 +3981,16 @@
           <t>https://github.com/JuliaLang/julia/compare/v1.12.7...v1.10.12</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>notas só com link; compare listado é v1.12.7...v1.10.12 (722 commits, base inversa), não isola a release; sem evidência legível</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2728,6 +4013,11 @@
           <t>https://github.com/JuliaLang/julia/compare/v1.10.12...v1.13.0</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2750,6 +4040,11 @@
           <t>https://github.com/axios/axios/compare/v0.30.2...v1.13.0</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2772,6 +4067,16 @@
           <t>https://github.com/axios/axios/compare/v1.13.6...v1.14.0</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>notas declaram que não há funcionalidade nova nem breaking changes</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2794,6 +4099,16 @@
           <t>https://github.com/axios/axios/compare/v0.31.0...v1.15.1</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>segurança e correções predominam; a seção New Features só traz scaffold de tradução de docs e um tipo TS (Location), sem funcionalidade de runtime</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2816,6 +4131,11 @@
           <t>https://github.com/axios/axios/compare/v0.32.0...v1.16.1</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2838,6 +4158,16 @@
           <t>https://github.com/axios/axios/compare/v1.17.0...v0.33.0</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>segurança predomina; o item "New Features" é só Node 26 na matriz de CI, não é funcionalidade do pacote</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2860,6 +4190,16 @@
           <t>https://github.com/debpalash/VoiceStudio/compare/v0.2.4...v0.2.6</t>
         </is>
       </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>notas "auto-generated"; commits decidem: predominam features e docs</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2882,6 +4222,11 @@
           <t>https://github.com/debpalash/VoiceStudio/compare/v0.2.7...v0.3.0</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2904,6 +4249,11 @@
           <t>https://github.com/debpalash/VoiceStudio/compare/v0.3.4...v0.3.5</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2926,6 +4276,16 @@
           <t>https://github.com/debpalash/VoiceStudio/compare/v0.3.15...v0.3.16</t>
         </is>
       </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>release de "qualidade", mas os commits são majoritariamente feat (mini-player, cache de segmentos, glossário)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2948,6 +4308,16 @@
           <t>https://github.com/debpalash/VoiceStudio/compare/v0.3.16...v0.3.17</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>seção Added (provisionamento de FFmpeg/yt-dlp, painel de áudio)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2965,6 +4335,16 @@
           <t>https://github.com/HKUDS/nanobot/releases/tag/v0.1.3.post4</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>primeira release da amostra sem anterior; notas anunciam funcionalidades</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2987,6 +4367,11 @@
           <t>https://github.com/HKUDS/nanobot/compare/v0.1.3.post4...v0.1.3.post5</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3009,6 +4394,11 @@
           <t>https://github.com/HKUDS/nanobot/compare/v0.1.4.post3...v0.1.4.post4</t>
         </is>
       </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3031,6 +4421,11 @@
           <t>https://github.com/HKUDS/nanobot/compare/v0.1.5.post3...v0.2.0</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3053,6 +4448,16 @@
           <t>https://github.com/HKUDS/nanobot/compare/v0.2.1...v0.2.2</t>
         </is>
       </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>headline é robustez, mas as notas também anunciam SDK/runtime e novas funções do WebUI</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3075,6 +4480,11 @@
           <t>https://github.com/facebookresearch/faiss/compare/v1.12.0...v1.13.0</t>
         </is>
       </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3097,6 +4507,11 @@
           <t>https://github.com/facebookresearch/faiss/compare/v1.13.0...v1.13.1</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3119,6 +4534,11 @@
           <t>https://github.com/facebookresearch/faiss/compare/v1.14.1...v1.14.2</t>
         </is>
       </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3141,6 +4561,11 @@
           <t>https://github.com/facebookresearch/faiss/compare/v1.14.3...v1.15.0</t>
         </is>
       </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3163,6 +4588,16 @@
           <t>https://github.com/facebookresearch/faiss/compare/v1.15.0...v1.15.1</t>
         </is>
       </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>notas só com link; commits misturam correções com funcionalidades (IDSelectorWithContext, build HNSW determinístico, SVE, C API)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3185,6 +4620,11 @@
           <t>https://github.com/Homebrew/brew/compare/4.6.15...4.6.16</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3207,6 +4647,16 @@
           <t>https://github.com/Homebrew/brew/compare/4.6.19...4.6.20</t>
         </is>
       </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>mistura correções com novo comando (brew lgtm)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3229,6 +4679,11 @@
           <t>https://github.com/Homebrew/brew/compare/5.0.16...5.1.0</t>
         </is>
       </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3251,6 +4706,16 @@
           <t>https://github.com/Homebrew/brew/compare/6.0.8...6.0.9</t>
         </is>
       </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>correções (cask/upgrade, install_steps) não predominam com clareza sobre desempenho, avisos novos e CI</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3273,6 +4738,11 @@
           <t>https://github.com/Homebrew/brew/compare/6.0.14...6.0.15</t>
         </is>
       </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3295,6 +4765,11 @@
           <t>https://github.com/coollabsio/coolify/compare/v4.0.0-beta.432...v4.0.0-beta.433</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3317,6 +4792,16 @@
           <t>https://github.com/coollabsio/coolify/compare/v4.0.0-beta.436...v4.0.0-beta.437</t>
         </is>
       </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>correção de segurança, mas as notas também anunciam melhorias de UI e de confiabilidade da API</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3339,6 +4824,16 @@
           <t>https://github.com/coollabsio/coolify/compare/v4.0.0-beta.454...v4.0.0-beta.455</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>seção Security &amp; Fixes, mas também novos templates de serviços e melhorias</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3361,6 +4856,11 @@
           <t>https://github.com/coollabsio/coolify/compare/v4.3.2...v4.3.3</t>
         </is>
       </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3383,6 +4883,11 @@
           <t>https://github.com/coollabsio/coolify/compare/v4.3.7...v4.3.8</t>
         </is>
       </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3405,6 +4910,11 @@
           <t>https://github.com/heygen-com/hyperframes/compare/v0.4.11...v0.4.12</t>
         </is>
       </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3427,6 +4937,11 @@
           <t>https://github.com/heygen-com/hyperframes/compare/v0.4.20...v0.4.21</t>
         </is>
       </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3449,6 +4964,11 @@
           <t>https://github.com/heygen-com/hyperframes/compare/v0.5.2...v0.5.3</t>
         </is>
       </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3471,6 +4991,11 @@
           <t>https://github.com/heygen-com/hyperframes/compare/v0.7.21...v0.7.22</t>
         </is>
       </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3493,6 +5018,11 @@
           <t>https://github.com/heygen-com/hyperframes/compare/v0.7.61...v0.7.62</t>
         </is>
       </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3515,6 +5045,11 @@
           <t>https://github.com/OpenHands/OpenHands/compare/0.57.2...0.58.0</t>
         </is>
       </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3537,6 +5072,11 @@
           <t>https://github.com/OpenHands/OpenHands/compare/1.0.2-cli...0.60.0</t>
         </is>
       </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3559,6 +5099,11 @@
           <t>https://github.com/OpenHands/OpenHands/compare/v1.6.1...v1.7.0</t>
         </is>
       </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3581,6 +5126,11 @@
           <t>https://github.com/OpenHands/OpenHands/compare/v1.18.0...v1.19.0</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3603,6 +5153,11 @@
           <t>https://github.com/OpenHands/OpenHands/compare/v1.22.0...v1.23.0</t>
         </is>
       </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3625,6 +5180,11 @@
           <t>https://github.com/toeverything/AFFiNE/compare/v0.24.1...v0.25.0</t>
         </is>
       </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3647,6 +5207,11 @@
           <t>https://github.com/toeverything/AFFiNE/compare/v0.25.7...v0.26.0</t>
         </is>
       </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3669,6 +5234,11 @@
           <t>https://github.com/toeverything/AFFiNE/compare/v0.26.3...v0.27.0</t>
         </is>
       </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3691,6 +5261,16 @@
           <t>https://github.com/toeverything/AFFiNE/compare/v0.27.0...v0.27.2</t>
         </is>
       </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>conteúdo é só correção (login, MCP); a seção Breaking change é aviso repetido da 0.27, não mudança desta release</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3713,6 +5293,16 @@
           <t>https://github.com/toeverything/AFFiNE/compare/v0.27.2...v0.27.3</t>
         </is>
       </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>anuncia coleta de lixo de documentos e melhorias, além de correções</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3735,6 +5325,11 @@
           <t>https://github.com/jestjs/jest/compare/v30.2.0...v30.3.0</t>
         </is>
       </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3757,6 +5352,11 @@
           <t>https://github.com/jestjs/jest/compare/v30.3.0...v30.4.0</t>
         </is>
       </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3779,6 +5379,16 @@
           <t>https://github.com/jestjs/jest/compare/v30.4.0...v30.4.1</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>correção de regressão, mas a seção Features anuncia opção nova de runner</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3801,6 +5411,11 @@
           <t>https://github.com/jestjs/jest/compare/v30.4.2...v30.5.0</t>
         </is>
       </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3823,6 +5438,11 @@
           <t>https://github.com/jestjs/jest/compare/v30.5.0...v30.5.1</t>
         </is>
       </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3845,6 +5465,16 @@
           <t>https://github.com/getsentry/sentry/compare/25.9.0...25.10.0</t>
         </is>
       </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>notas geradas, dominadas por New Features e Internal Changes</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3867,6 +5497,16 @@
           <t>https://github.com/getsentry/sentry/compare/25.10.0...25.11.0</t>
         </is>
       </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>notas geradas, dominadas por New Features e Internal Changes</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3889,6 +5529,16 @@
           <t>https://github.com/getsentry/sentry/compare/26.2.1...26.3.0</t>
         </is>
       </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>notas geradas, dominadas por New Features e Internal Changes</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3911,6 +5561,16 @@
           <t>https://github.com/getsentry/sentry/compare/26.4.2...26.5.0</t>
         </is>
       </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>notas geradas, dominadas por New Features e Internal Changes</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3933,6 +5593,16 @@
           <t>https://github.com/getsentry/sentry/compare/26.5.1...26.5.2</t>
         </is>
       </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>notas geradas, dominadas por New Features e Internal Changes</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3955,6 +5625,16 @@
           <t>https://github.com/redis/redis/compare/8.2.4...8.4.1</t>
         </is>
       </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>compare cobre vários patches (8.2.4...8.4.1); decidido pelas notas, que são só Security fixes e Bug fixes</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3977,6 +5657,16 @@
           <t>https://github.com/redis/redis/compare/7.4.8...7.2.13</t>
         </is>
       </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>compare com base invertida; decidido pelas notas (só correção de segurança)</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3999,6 +5689,11 @@
           <t>https://github.com/redis/redis/compare/7.2.16...7.4.11</t>
         </is>
       </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4021,6 +5716,11 @@
           <t>https://github.com/redis/redis/compare/8.2.9...8.4.6</t>
         </is>
       </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4043,6 +5743,16 @@
           <t>https://github.com/redis/redis/compare/8.10.1...8.2.10</t>
         </is>
       </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>correção de segurança do cluster bus inclui opção de configuração nova, parte da própria correção</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4065,6 +5775,16 @@
           <t>https://github.com/supabase/supabase/compare/1.25.04...1.25.12</t>
         </is>
       </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>resumo mensal de novidades do produto; compare cobre centenas de commits</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4087,6 +5807,16 @@
           <t>https://github.com/supabase/supabase/compare/1.25.12...v1.26.01</t>
         </is>
       </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>resumo mensal de novidades do produto; compare cobre centenas de commits</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4109,6 +5839,16 @@
           <t>https://github.com/supabase/supabase/compare/v1.26.01...v1.26.02</t>
         </is>
       </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>resumo mensal de novidades do produto; compare cobre centenas de commits</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4131,6 +5871,16 @@
           <t>https://github.com/supabase/supabase/compare/v1.26.04...v1.26.05</t>
         </is>
       </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>resumo mensal de novidades do produto; compare cobre centenas de commits</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4153,6 +5903,16 @@
           <t>https://github.com/supabase/supabase/compare/v1.26.07...v1.26.08</t>
         </is>
       </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>resumo mensal de novidades do produto; compare cobre centenas de commits</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4175,6 +5935,16 @@
           <t>https://github.com/exelban/stats/compare/v2.12.0...v2.12.1</t>
         </is>
       </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>correções, mas as notas têm seção New features</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4197,6 +5967,11 @@
           <t>https://github.com/exelban/stats/compare/v2.12.4...v2.12.5</t>
         </is>
       </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4219,6 +5994,16 @@
           <t>https://github.com/exelban/stats/compare/v3.0.14...v3.0.15</t>
         </is>
       </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>correções predominam, mas as notas anunciam funcionalidades novas (Text widget na GPU)</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4241,6 +6026,11 @@
           <t>https://github.com/exelban/stats/compare/v3.0.15...v3.0.16</t>
         </is>
       </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4263,6 +6053,16 @@
           <t>https://github.com/exelban/stats/compare/v3.0.17...v3.0.18</t>
         </is>
       </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>seis correções, mas as notas têm seção New features</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4285,6 +6085,16 @@
           <t>https://github.com/llvm/llvm-project/compare/llvmorg-21.1.2...llvmorg-21.1.3</t>
         </is>
       </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>notas só com links de download; commits do compare são backports predominantemente de correção</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4307,6 +6117,16 @@
           <t>https://github.com/llvm/llvm-project/compare/llvmorg-21.1.3...llvmorg-21.1.4</t>
         </is>
       </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>notas só com links de download; commits do compare são backports predominantemente de correção</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4329,6 +6149,16 @@
           <t>https://github.com/llvm/llvm-project/compare/llvmorg-21.1.5...llvmorg-21.1.6</t>
         </is>
       </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>notas só com links de download; commits do compare são backports predominantemente de correção</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4351,6 +6181,16 @@
           <t>https://github.com/llvm/llvm-project/compare/llvmorg-21.1.7...llvmorg-21.1.8</t>
         </is>
       </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>notas só com links de download; commits do compare são backports predominantemente de correção</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4373,6 +6213,16 @@
           <t>https://github.com/llvm/llvm-project/compare/llvmorg-22.1.1...llvmorg-22.1.2</t>
         </is>
       </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>notas só com links de download; commits do compare são backports predominantemente de correção</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4395,6 +6245,11 @@
           <t>https://github.com/makeplane/plane/compare/v1.0.0...v1.1.0</t>
         </is>
       </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4417,6 +6272,11 @@
           <t>https://github.com/makeplane/plane/compare/v1.1.0...v1.2.0</t>
         </is>
       </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4439,6 +6299,11 @@
           <t>https://github.com/makeplane/plane/compare/v1.2.3...v1.3.0</t>
         </is>
       </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4461,6 +6326,11 @@
           <t>https://github.com/makeplane/plane/compare/v1.3.1...v1.4.0</t>
         </is>
       </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4483,6 +6353,16 @@
           <t>https://github.com/makeplane/plane/compare/v1.4.0...v1.4.1</t>
         </is>
       </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>correções e segurança, mas a seção Features anuncia comando novo</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4505,6 +6385,16 @@
           <t>https://github.com/microsoft/monaco-editor/compare/v0.53.0...v0.54.0</t>
         </is>
       </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>lista de PRs majoritariamente de build, mirrors e samples; correções não predominam</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4527,6 +6417,16 @@
           <t>https://github.com/microsoft/monaco-editor/compare/v0.54.0...v0.55.0</t>
         </is>
       </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>PRs de pipeline, website e dependências</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4549,6 +6449,11 @@
           <t>https://github.com/microsoft/monaco-editor/compare/v0.55.0...v0.55.1</t>
         </is>
       </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4571,6 +6476,16 @@
           <t>https://github.com/microsoft/monaco-editor/compare/v0.55.1...v0.56.0</t>
         </is>
       </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>majoritariamente bumps de dependência e CI; sem correção de defeito predominante</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4593,6 +6508,16 @@
           <t>https://github.com/microsoft/monaco-editor/compare/v0.56.0...v0.57.0</t>
         </is>
       </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>majoritariamente bumps de dependência</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4615,6 +6540,16 @@
           <t>https://github.com/langchain-ai/langchain/compare/langchain-core%3D%3D1.0.0rc3...langchain%3D%3D1.0.0rc2</t>
         </is>
       </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>release candidate; o compare traz commit de feature (middleware Anthropic)</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4637,6 +6572,16 @@
           <t>https://github.com/langchain-ai/langchain/compare/langchain-anthropic%3D%3D1.0.0...langchain-text-splitters%3D%3D1.0.0</t>
         </is>
       </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>release 1.0.0 com notas de docs/estilo/chore</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4659,6 +6604,16 @@
           <t>https://github.com/langchain-ai/langchain/compare/langchain-groq%3D%3D1.1.2...langchain-anthropic%3D%3D1.3.2</t>
         </is>
       </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>commits "fix" na verdade adicionam suporte a recursos novos (output_config, compaction), sem defeito descrito; na dúvida, não</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4681,6 +6636,16 @@
           <t>https://github.com/langchain-ai/langchain/compare/langchain-perplexity%3D%3D1.3.1...langchain-anthropic%3D%3D1.4.4</t>
         </is>
       </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>um único ajuste de código (normalização de IDs de tool-call entre provedores); o resto é teste e dependências</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4703,6 +6668,11 @@
           <t>https://github.com/langchain-ai/langchain/compare/langchain%3D%3D1.3.16...langchain-fireworks%3D%3D1.6.0</t>
         </is>
       </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4725,6 +6695,11 @@
           <t>https://github.com/crewAIInc/crewAI/compare/0.201.1...0.203.0</t>
         </is>
       </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4747,6 +6722,11 @@
           <t>https://github.com/crewAIInc/crewAI/compare/1.2.0...1.2.1</t>
         </is>
       </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4769,6 +6749,11 @@
           <t>https://github.com/crewAIInc/crewAI/compare/1.15.11...1.15.12</t>
         </is>
       </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4791,6 +6776,11 @@
           <t>https://github.com/crewAIInc/crewAI/compare/1.15.17...1.15.18</t>
         </is>
       </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4813,6 +6803,16 @@
           <t>https://github.com/crewAIInc/crewAI/compare/1.15.18...1.15.19</t>
         </is>
       </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>muitas correções, mas a seção Features anuncia novas integrações</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4835,6 +6835,11 @@
           <t>https://github.com/rust-lang/rust/compare/1.90.0...1.91.0</t>
         </is>
       </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4857,6 +6862,11 @@
           <t>https://github.com/rust-lang/rust/compare/1.93.1...1.94.0</t>
         </is>
       </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4879,6 +6889,11 @@
           <t>https://github.com/rust-lang/rust/compare/1.96.0...1.96.1</t>
         </is>
       </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4901,6 +6916,11 @@
           <t>https://github.com/rust-lang/rust/compare/1.97.0...1.97.1</t>
         </is>
       </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4923,6 +6943,11 @@
           <t>https://github.com/rust-lang/rust/compare/1.97.1...1.98.0</t>
         </is>
       </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4945,6 +6970,16 @@
           <t>https://github.com/ggml-org/llama.cpp/compare/b7077...b7078</t>
         </is>
       </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>sem notas; o commit único ("handle context overflow during decode") não afirma corrigir defeito, então, na dúvida, não</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4967,6 +7002,11 @@
           <t>https://github.com/ggml-org/llama.cpp/compare/b7219...b7220</t>
         </is>
       </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4989,6 +7029,11 @@
           <t>https://github.com/ggml-org/llama.cpp/compare/b9128...b9129</t>
         </is>
       </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5011,6 +7056,11 @@
           <t>https://github.com/ggml-org/llama.cpp/compare/b9753...b9754</t>
         </is>
       </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5033,6 +7083,11 @@
           <t>https://github.com/ggml-org/llama.cpp/compare/v0.4.0...v0.4.1</t>
         </is>
       </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5055,6 +7110,16 @@
           <t>https://github.com/metabase/metabase/compare/v0.56.18...v0.56.19</t>
         </is>
       </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>notas sem mudanças; 7 commits: metade CI, e entre as mudanças de produto as correções (2) não predominam sobre desempenho e UX</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5077,6 +7142,16 @@
           <t>https://github.com/metabase/metabase/compare/v0.54.23...v0.55.23</t>
         </is>
       </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>compare listado é v0.54.23...v0.55.23 (1716 commits entre linhas de versão), não isola a release; notas sem mudanças</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5099,6 +7174,16 @@
           <t>https://github.com/metabase/metabase/compare/v0.61.2...v0.60.7</t>
         </is>
       </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>compare listado é v0.61.2...v0.60.7 (base de outra linha, 463 commits) e inclui backports de funcionalidade; notas sem mudanças</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5121,6 +7206,16 @@
           <t>https://github.com/metabase/metabase/compare/v0.62.2...v0.58.18</t>
         </is>
       </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>compare listado é v0.62.2...v0.58.18 (base de outra linha, 647 commits), não isola a release; notas sem mudanças</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5143,6 +7238,16 @@
           <t>https://github.com/metabase/metabase/compare/v0.59.19...v0.58.22</t>
         </is>
       </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>compare listado é v0.59.19...v0.58.22 (base de outra linha, 707 commits), não isola a release; notas sem mudanças</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -5165,6 +7270,16 @@
           <t>https://github.com/cline/cline/compare/v3.44.0...v3.44.1</t>
         </is>
       </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>duas correções, mas as notas anunciam suporte novo a instruções dinâmicas de ferramenta</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5187,6 +7302,11 @@
           <t>https://github.com/cline/cline/compare/v4.1.6...desktop-v0.0.10</t>
         </is>
       </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5209,6 +7329,16 @@
           <t>https://github.com/cline/cline/compare/v4.1.7...desktop-v0.0.11</t>
         </is>
       </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>muitas correções, mas anuncia colar imagens da área de transferência</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5231,6 +7361,16 @@
           <t>https://github.com/cline/cline/compare/sdk/sdk/v0.0.79...cli-v3.0.58</t>
         </is>
       </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>mistura limite de log, catálogo de modelos com novos provedores e ajuste de diálogo</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -5253,6 +7393,11 @@
           <t>https://github.com/cline/cline/compare/cli-v3.0.61...desktop-v0.0.22</t>
         </is>
       </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5275,6 +7420,16 @@
           <t>https://github.com/yt-dlp/yt-dlp/compare/2025.09.26...2025.10.14</t>
         </is>
       </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>correções de extratores convivem com ao menos seis extratores/recursos novos (idagio, listen do cbc/abc, impersonation do tiktok)</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5297,6 +7452,16 @@
           <t>https://github.com/yt-dlp/yt-dlp/compare/2026.01.29...2026.01.31</t>
         </is>
       </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>mais itens de recurso (soop, whyp, fallback web_embedded) do que correção; remoção de clientes quebrados é só parte</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -5319,6 +7484,16 @@
           <t>https://github.com/yt-dlp/yt-dlp/compare/2026.03.03...2026.03.13</t>
         </is>
       </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>quase tudo é conserto de tiktok e clientes do youtube; só uma configuração de cliente e bump de dependência fogem disso</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5341,6 +7516,16 @@
           <t>https://github.com/yt-dlp/yt-dlp/compare/2026.03.17...2026.06.09</t>
         </is>
       </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>mistura grande de correções de segurança e extratores com vários recursos novos e mudanças de requisitos</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -5363,6 +7548,16 @@
           <t>https://github.com/yt-dlp/yt-dlp/compare/2026.06.09...2026.07.04</t>
         </is>
       </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>muitas correções e uma de segurança, mas também dezenas de recursos/extratores novos e mudança de versão mínima do Python</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -5380,6 +7575,16 @@
           <t>https://github.com/rtk-ai/rtk/releases/tag/v0.2.0</t>
         </is>
       </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>primeira release do repositório, sem anterior; notas só com link de changelog</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -5402,6 +7607,11 @@
           <t>https://github.com/rtk-ai/rtk/compare/v0.8.0...v0.8.1</t>
         </is>
       </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5424,6 +7634,16 @@
           <t>https://github.com/rtk-ai/rtk/compare/v0.13.0...v0.13.1</t>
         </is>
       </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>muda apenas o workflow de CI que não subia os artefatos; CI não entra como defeito do projeto</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -5446,6 +7666,11 @@
           <t>https://github.com/rtk-ai/rtk/compare/v0.39.0...v0.40.0</t>
         </is>
       </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5468,6 +7693,11 @@
           <t>https://github.com/rtk-ai/rtk/compare/v0.44.1...v0.44.2</t>
         </is>
       </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -5490,6 +7720,16 @@
           <t>https://github.com/denoland/deno/compare/v2.7.6...v2.7.7</t>
         </is>
       </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>11 de 12 itens são correções de compatibilidade e estabilidade</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -5512,6 +7752,16 @@
           <t>https://github.com/denoland/deno/compare/v2.7.7...v2.7.8</t>
         </is>
       </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>50 de 58 itens são correções; só seis recursos pontuais (exporter OTel, P-521, domínio CDP)</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -5534,6 +7784,16 @@
           <t>https://github.com/denoland/deno/compare/v2.8.1...v2.8.2</t>
         </is>
       </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>abre com recursos relevantes (--bundle/--minify, ML-DSA/ML-KEM, proxy no node:http) apesar de longa lista de correções</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -5556,6 +7816,16 @@
           <t>https://github.com/denoland/deno/compare/v2.8.3...v2.9.0</t>
         </is>
       </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>release de recursos: deno desktop, watch, link, test --shard, snapshots</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -5578,6 +7848,16 @@
           <t>https://github.com/denoland/deno/compare/v2.9.0...v2.9.1</t>
         </is>
       </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>patch de 2.9.0: três itens de recurso contra dezenas de correções (desktop, npm, LSP)</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -5600,6 +7880,16 @@
           <t>https://github.com/modelcontextprotocol/servers/compare/2025.9.25...2025.11.25</t>
         </is>
       </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>notas só listam pacotes; commits incluem servidor novo e mudança de formato da memória</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -5622,6 +7912,16 @@
           <t>https://github.com/modelcontextprotocol/servers/compare/2025.11.25...2025.12.18</t>
         </is>
       </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>commits majoritariamente de documentação e README</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -5644,6 +7944,16 @@
           <t>https://github.com/modelcontextprotocol/servers/compare/2025.12.18...2026.1.14</t>
         </is>
       </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>refatoração do servidor everything</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -5666,6 +7976,16 @@
           <t>https://github.com/modelcontextprotocol/servers/compare/2026.7.4...2026.7.10</t>
         </is>
       </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>únicas mudanças de código são correções no filesystem e CVE; o resto é docs e dependências</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -5688,6 +8008,11 @@
           <t>https://github.com/modelcontextprotocol/servers/compare/2026.8.18...2026.8.31</t>
         </is>
       </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -5710,6 +8035,16 @@
           <t>https://github.com/opendatalab/MinerU/compare/mineru-2.5.4-released...mineru-2.6.2-released</t>
         </is>
       </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>otimizações e recursos (fórmulas em chinês, mesclagem de tabelas)</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -5732,6 +8067,16 @@
           <t>https://github.com/opendatalab/MinerU/compare/mineru-2.6.6-released...mineru-2.6.7-released</t>
         </is>
       </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>nota única: correção do bug #4168</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -5754,6 +8099,16 @@
           <t>https://github.com/opendatalab/MinerU/compare/mineru-3.4.4-released...mineru-3.4.5-released</t>
         </is>
       </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>duas correções (tabelas docx descartadas, surrogate pairs no PDF)</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -5776,6 +8131,16 @@
           <t>https://github.com/opendatalab/MinerU/compare/mineru-4.0.4-released...mineru-4.0.5-released</t>
         </is>
       </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>seções Features e Dependencies; sem correção</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -5798,6 +8163,16 @@
           <t>https://github.com/opendatalab/MinerU/compare/mineru-4.0.5-released...mineru-4.0.6-released</t>
         </is>
       </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>abre com preview de EPUB na WebUI; as duas correções acompanham o recurso</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -5820,6 +8195,16 @@
           <t>https://github.com/astral-sh/uv/compare/0.10.12...0.11.0</t>
         </is>
       </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>mudanças de rede/certificado, recursos e preview</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -5842,6 +8227,16 @@
           <t>https://github.com/astral-sh/uv/compare/0.11.9...0.11.10</t>
         </is>
       </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>única mudança: correção em pedido de Python pré-release</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -5864,6 +8259,16 @@
           <t>https://github.com/astral-sh/uv/compare/0.11.20...0.11.21</t>
         </is>
       </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>cerca de 22 correções de robustez contra poucos itens de recurso (CPython novo, previews)</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -5886,6 +8291,16 @@
           <t>https://github.com/astral-sh/uv/compare/0.11.21...0.11.22</t>
         </is>
       </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>recursos (publish, check, audit SARIF) abrem a nota; correções são maioria numérica mas misturadas</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -5908,6 +8323,16 @@
           <t>https://github.com/astral-sh/uv/compare/0.12.4...0.12.5</t>
         </is>
       </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>novas versões de CPython e recursos em preview superam a correção única</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -5925,6 +8350,16 @@
           <t>https://github.com/tinyhumansai/openhuman/releases/tag/v0.49.32</t>
         </is>
       </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>lista de PRs com quase o mesmo número de recursos e correções, além de refatorações; fase inicial de construção</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -5947,6 +8382,16 @@
           <t>https://github.com/tinyhumansai/openhuman/compare/v0.51.5...v0.51.6</t>
         </is>
       </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>três itens de recurso (presets de IA local, tipos de entidade na memória, tema claro) contra correções só de e2e</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -5969,6 +8414,16 @@
           <t>https://github.com/tinyhumansai/openhuman/compare/v0.52.6...v0.52.7</t>
         </is>
       </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>página sem corpo de notas e sem acesso à comparação de commits; sem evidência de correção, mantido como não</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -5991,6 +8446,16 @@
           <t>https://github.com/tinyhumansai/openhuman/compare/v0.53.22...v0.53.35</t>
         </is>
       </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>nota longa com muitas correções, porém abre com carteira/seed phrase, ingestão de transcrições e autoatualização; limítrofe</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -6013,6 +8478,16 @@
           <t>https://github.com/tinyhumansai/openhuman/compare/v0.57.53...v0.58.0</t>
         </is>
       </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>highlights de memória, tarefas e integrações; correções são apenas um dos quatro eixos</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -6035,6 +8510,16 @@
           <t>https://github.com/microsoft/playwright/compare/v1.55.1...v1.56.0</t>
         </is>
       </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>agentes Playwright e APIs novas</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -6057,6 +8542,16 @@
           <t>https://github.com/microsoft/playwright/compare/v1.58.1...v1.58.2</t>
         </is>
       </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>patch com duas correções (trace viewer, SwiftShader no macOS)</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -6079,6 +8574,16 @@
           <t>https://github.com/microsoft/playwright/compare/v1.60.0...v1.61.0</t>
         </is>
       </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>passkeys WebAuthn, Web Storage e várias APIs novas</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -6101,6 +8606,16 @@
           <t>https://github.com/microsoft/playwright/compare/v1.61.1...v1.62.0</t>
         </is>
       </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>novo modelo de component testing, cancelamento, WebP; nenhuma correção</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -6123,6 +8638,16 @@
           <t>https://github.com/microsoft/playwright/compare/v1.62.0...v1.62.1</t>
         </is>
       </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>nota só com Bug Fixes (regressões de tsconfig, snapshot de acessibilidade)</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -6145,6 +8670,16 @@
           <t>https://github.com/bitcoin/bitcoin/compare/v29.1...v30.0</t>
         </is>
       </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>notas abrem com novo comando bitcoin, interface IPC de mineração, mudanças de política e remoções; correções são minoria</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -6167,6 +8702,16 @@
           <t>https://github.com/bitcoin/bitcoin/compare/v29.2...v28.3</t>
         </is>
       </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>"various bug fixes and performance improvements"; única mudança de comportamento é a redução de taxas mínimas padrão</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -6189,6 +8734,16 @@
           <t>https://github.com/bitcoin/bitcoin/compare/v30.2...v29.3</t>
         </is>
       </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>correções de migração de carteira, overflow na mineração e build; um item de melhoria na carteira e dois de desempenho</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -6211,6 +8766,16 @@
           <t>https://github.com/bitcoin/bitcoin/compare/v31.1...v30.3</t>
         </is>
       </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>nenhuma funcionalidade nova; correções de build/carteira/validação e manutenção de testes, docs e CI</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -6233,6 +8798,16 @@
           <t>https://github.com/bitcoin/bitcoin/compare/v30.3...v29.4</t>
         </is>
       </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>correções e ajustes de desempenho do chainstate; nenhuma funcionalidade nova</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -6255,6 +8830,16 @@
           <t>https://github.com/puppeteer/puppeteer/compare/puppeteer-v24.28.0...puppeteer-core-v24.28.0</t>
         </is>
       </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>um recurso (orientação de tela via BiDi) e uma correção (erro em snapshot de iframe), mais docs e chores</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -6277,6 +8862,16 @@
           <t>https://github.com/puppeteer/puppeteer/compare/puppeteer-core-v24.32.0...browsers-v2.11.0</t>
         </is>
       </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>dois recursos (diretório de dados do Chrome, canal em connect) e uma correção de separador de caminho</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -6299,6 +8894,16 @@
           <t>https://github.com/puppeteer/puppeteer/compare/puppeteer-core-v24.34.0...puppeteer-v24.35.0</t>
         </is>
       </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>só sincronização de versões e bump de dependências, sem correção</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -6321,6 +8926,16 @@
           <t>https://github.com/puppeteer/puppeteer/compare/puppeteer-core-v24.37.2...puppeteer-v24.37.3</t>
         </is>
       </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>só chores e bump de dependências; nada que corrija comportamento</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -6343,6 +8958,16 @@
           <t>https://github.com/puppeteer/puppeteer/compare/browsers-v3.2.0...puppeteer-v25.7.0</t>
         </is>
       </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>atualização da versão-alvo do Chrome (listada como recurso) e bump de dependência</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -6360,6 +8985,16 @@
           <t>https://github.com/vectorize-io/hindsight/releases/tag/v0.0.16</t>
         </is>
       </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>notas só trazem instruções de instalação e imagens; nada indica correção</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -6382,6 +9017,16 @@
           <t>https://github.com/vectorize-io/hindsight/compare/v0.1.0...v0.1.1</t>
         </is>
       </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>notas só trazem instruções de instalação e imagens; nada indica correção</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -6404,6 +9049,16 @@
           <t>https://github.com/vectorize-io/hindsight/compare/v0.3.0...v0.4.0</t>
         </is>
       </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>cerca de 14 recursos (mental models, worker, JSON logging) contra 15 correções e vários itens de docs</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -6426,6 +9081,16 @@
           <t>https://github.com/vectorize-io/hindsight/compare/v0.5.3...v0.5.4</t>
         </is>
       </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>quase todos os itens de código são correções (retries, idioma, duplicatas, worker, reflect); recursos são pontuais (CLI de workers, batch de embeddings)</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -6448,6 +9113,16 @@
           <t>https://github.com/vectorize-io/hindsight/compare/v0.6.2...v0.7.0</t>
         </is>
       </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>90 itens com dezenas de recursos (provedores, pg_search, i18n, endpoints) ao lado das correções</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -6465,6 +9140,16 @@
           <t>https://github.com/abhigyanpatwari/GitNexus/releases/tag/v1.3.10</t>
         </is>
       </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>seções de segurança/correção pequenas, mas a nota inclui lista grande de recursos (PHP, Swift, Kotlin, plugin, modo remoto)</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -6487,6 +9172,16 @@
           <t>https://github.com/abhigyanpatwari/GitNexus/compare/v1.4.9...v1.4.10</t>
         </is>
       </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>só correção: conflito de peer dependencies do tree-sitter que quebrava o npx do MCP</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -6509,6 +9204,16 @@
           <t>https://github.com/abhigyanpatwari/GitNexus/compare/v1.5.1...v1.5.2</t>
         </is>
       </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>só correção: instalação global falhava por pacote de workspace não publicado</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -6531,6 +9236,16 @@
           <t>https://github.com/abhigyanpatwari/GitNexus/compare/v1.6.2...v1.6.3</t>
         </is>
       </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>16 itens de Added (análise entre repositórios, comandos, Docker) ao lado de 17 correções</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -6553,6 +9268,16 @@
           <t>https://github.com/abhigyanpatwari/GitNexus/compare/v1.6.10...v1.6.11</t>
         </is>
       </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>highlights são recursos (Zig, notificações, watch, Spring); correções vêm depois</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -6575,6 +9300,16 @@
           <t>https://github.com/openbq-org/OpenBB/compare/4.4.5...v4.5.0</t>
         </is>
       </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Python 3.13, Congress.gov, refatoração da FMP e quebras de compatibilidade; só três correções</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -6597,6 +9332,16 @@
           <t>https://github.com/openbq-org/OpenBB/compare/v4.5.0...Open-Data-Platform-v1.0.0</t>
         </is>
       </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>notas de uma linha ("releases version 1.0.0 of the Desktop Application"); sem sinal de correção</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -6619,6 +9364,16 @@
           <t>https://github.com/openbq-org/OpenBB/compare/v4.7.0...Open-Data-Platform-v1.0.2</t>
         </is>
       </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>um recurso (botão de limpar logs) e uma atualização de openssl/remoção de binários; equilibrado e pequeno</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -6641,6 +9396,16 @@
           <t>https://github.com/openbq-org/OpenBB/compare/Open-Data-Platform-v2.0.0...ODP</t>
         </is>
       </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>tag móvel que aponta para a versão estável do desktop; notas só remetem à página da versão</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -6663,6 +9428,16 @@
           <t>https://github.com/openbq-org/OpenBB/compare/ODP...openbb-v5.0.0</t>
         </is>
       </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>salto de versão maior: novo CLI 2.0, streaming, mudança de licença, remoção de provedores e quebras de compatibilidade</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -6685,6 +9460,16 @@
           <t>https://github.com/MHSanaei/3x-ui/compare/v2.8.8...v2.8.9</t>
         </is>
       </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>seis recursos (XHTTP, Finalmask, Hysteria) contra quatro correções</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -6707,6 +9492,16 @@
           <t>https://github.com/MHSanaei/3x-ui/compare/v2.9.4...v3.1.0</t>
         </is>
       </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>reescrita do frontend em React e vários recursos novos, ao lado de muitas correções</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -6729,6 +9524,16 @@
           <t>https://github.com/MHSanaei/3x-ui/compare/v3.2.0...v3.2.5</t>
         </is>
       </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>abre com recursos (backup Postgres, atualização em massa de nós), apesar da lista longa de correções</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -6751,6 +9556,16 @@
           <t>https://github.com/MHSanaei/3x-ui/compare/v3.3.1...v3.4.0</t>
         </is>
       </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>notificações, Managed Hosts, fail2ban, pinning TLS: release de recursos</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -6773,6 +9588,16 @@
           <t>https://github.com/MHSanaei/3x-ui/compare/v3.5.0...v3.6.0</t>
         </is>
       </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>cerca de 70 correções (auditorias, assinaturas, nós, segurança) contra 11 itens pequenos de recurso; limítrofe pelo redesenho do dashboard</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -6795,6 +9620,16 @@
           <t>https://github.com/TryGhost/Ghost/compare/v6.10.1...v6.10.2</t>
         </is>
       </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>nota diz "minor bug fixes for issues Ghost users reported"</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -6817,6 +9652,16 @@
           <t>https://github.com/TryGhost/Ghost/compare/v6.19.3...v6.19.4</t>
         </is>
       </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>quatro correções (upload, permissões, last_seen, filtro) mais tradução e otimização de consulta</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -6839,6 +9684,16 @@
           <t>https://github.com/TryGhost/Ghost/compare/v6.37.1...v6.38.0</t>
         </is>
       </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>um helper novo (social_accounts) ao lado de duas correções; muito pequeno para afirmar predomínio de correção</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -6861,6 +9716,16 @@
           <t>https://github.com/TryGhost/Ghost/compare/v6.52.1...v6.53.0</t>
         </is>
       </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>três recursos/melhorias de adapters e anti-spam contra duas correções</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -6883,6 +9748,16 @@
           <t>https://github.com/TryGhost/Ghost/compare/v6.63.0...v6.64.0</t>
         </is>
       </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>cinco correções (ícones, CSS malformado, newsletters, auditoria, import) e atualização do tema Source</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -6905,6 +9780,16 @@
           <t>https://github.com/usememos/memos/compare/v0.25.1...v0.25.2</t>
         </is>
       </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>oito recursos de interface (masonry, tema automático, thumbnails S3) contra quatro correções</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -6927,6 +9812,16 @@
           <t>https://github.com/usememos/memos/compare/v0.26.2...v0.27.0</t>
         </is>
       </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>release de recursos (servidor MCP, IA/voz, links de compartilhamento) com lista longa de correções agregada</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -6949,6 +9844,16 @@
           <t>https://github.com/usememos/memos/compare/v0.28.0...v0.29.0</t>
         </is>
       </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>recursos (prévia de links, SMTP, atalhos) e correções em quantidade parecida; recursos abrem a nota</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -6971,6 +9876,16 @@
           <t>https://github.com/usememos/memos/compare/v0.29.0...v0.29.1</t>
         </is>
       </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>só Bug Fixes: alinhamento de tarefas, prévia de links e miniaturas de vídeo</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -6993,6 +9908,16 @@
           <t>https://github.com/usememos/memos/compare/v0.29.1...v0.30.0</t>
         </is>
       </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>web clipper, novo editor CodeMirror 6 e mudanças incompatíveis</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -7015,6 +9940,16 @@
           <t>https://github.com/jgm/pandoc/compare/3.8.1...3.8.2</t>
         </is>
       </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>abre com a extensão table_attributes (ativa por padrão); três correções pequenas do writer Typst/LaTeX acompanham</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -7037,6 +9972,16 @@
           <t>https://github.com/jgm/pandoc/compare/3.8.2.1...3.8.3</t>
         </is>
       </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>novos formatos de entrada (AsciiDoc, xlsx, pptx) e saída BBCode, junto de várias correções</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -7059,6 +10004,16 @@
           <t>https://github.com/jgm/pandoc/compare/3.9.0.1...3.9.0.2</t>
         </is>
       </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>única mudança: regressão do template Typst da 3.9.0.1</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -7081,6 +10036,16 @@
           <t>https://github.com/jgm/pandoc/compare/3.10.2...3.11</t>
         </is>
       </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>--math-method, MathML padrão, completions e RTL no ODT/Docx; as correções são numerosas, mas a nota abre com recursos</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -7103,6 +10068,16 @@
           <t>https://github.com/jgm/pandoc/compare/3.11...3.12</t>
         </is>
       </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>foco em desempenho com recursos pontuais (modo escuro, XML standalone) e muitas correções de leitores/escritores</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -7125,6 +10100,16 @@
           <t>https://github.com/mermaid-js/mermaid/compare/mermaid@11.13.0...@mermaid-js/tiny@11.13.0</t>
         </is>
       </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Minor Changes trazem diagramas novos (venn, ishikawa) e setas; a lista longa de correções vem em patch</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -7147,6 +10132,16 @@
           <t>https://github.com/mermaid-js/mermaid/compare/@mermaid-js/parser@1.1.0...@mermaid-js/tiny@11.14.0</t>
         </is>
       </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Wardley Maps, TreeView e visual Neo em vários diagramas</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -7169,6 +10164,16 @@
           <t>https://github.com/mermaid-js/mermaid/compare/mermaid@12.0.0...@mermaid-js/examples@2.0.0</t>
         </is>
       </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>major: eleva requisitos mínimos (ES2024, Safari 17.4, Node 22.12) e adiciona diagrama de casos de uso</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -7191,6 +10196,16 @@
           <t>https://github.com/mermaid-js/mermaid/compare/@mermaid-js/examples@2.0.0...@mermaid-js/mermaid-zenuml@1.0.0</t>
         </is>
       </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>major com mudança de requisitos mínimos e atualização de dependências</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -7213,6 +10228,16 @@
           <t>https://github.com/mermaid-js/mermaid/compare/@mermaid-js/tiny@12.0.0...@mermaid-js/mermaid-zenuml@1.0.1</t>
         </is>
       </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>patch único para o plugin funcionar com Mermaid 12; é adaptação de compatibilidade e a nota o lista como recurso, então não afirmei correção</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -7235,6 +10260,16 @@
           <t>https://github.com/outline/outline/compare/v0.87.4...v1.0.0</t>
         </is>
       </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>lightbox, menções de grupo, PlantUML e mudanças de API, ao lado de lista longa de correções</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -7257,6 +10292,16 @@
           <t>https://github.com/outline/outline/compare/v1.0.0...v1.0.1</t>
         </is>
       </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>só seção Fixes: seleção de imagens, matemática inline, randomUUID sem SSL, embeds do YouTube</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -7279,6 +10324,16 @@
           <t>https://github.com/outline/outline/compare/v1.1.0...v1.2.0</t>
         </is>
       </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>diagrams.net, emoji personalizado, passkeys e outros recursos de destaque</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -7301,6 +10356,16 @@
           <t>https://github.com/outline/outline/compare/v1.3.0...v1.4.0</t>
         </is>
       </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>destaques são recursos (toggle blocks, cor de célula, destaque de busca), apesar de muitas correções</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -7323,6 +10388,16 @@
           <t>https://github.com/outline/outline/compare/v1.6.0...v1.6.1</t>
         </is>
       </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>seis correções pontuais contra cinco itens de recurso (MCP, ícones PWA, doc aninhado)</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -7345,6 +10420,16 @@
           <t>https://github.com/agno-agi/agno/compare/v2.2.7...v2.2.8</t>
         </is>
       </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>único conserto: Redis deixa de ser dependência obrigatória (mais bump de versão)</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -7367,6 +10452,16 @@
           <t>https://github.com/agno-agi/agno/compare/v2.3.5...v2.3.6</t>
         </is>
       </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>quatro correções (session_state, sessões vazias, evals, tópicos de memória) contra um toolkit novo do Spotify</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -7389,6 +10484,16 @@
           <t>https://github.com/agno-agi/agno/compare/v2.3.14...v2.3.15</t>
         </is>
       </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>abre com custo de runs no OpenRouter e endpoint de migração de bancos; quatro correções acompanham</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -7411,6 +10516,16 @@
           <t>https://github.com/agno-agi/agno/compare/v2.4.2...v2.4.3</t>
         </is>
       </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>ExcelReader e registry no demo ao lado de correções de eventos e reasoning; recurso é real, não só detalhe</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -7433,6 +10548,16 @@
           <t>https://github.com/agno-agi/agno/compare/v2.6.18...v2.6.19</t>
         </is>
       </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>checkpointing, forking de sessão e StudioTool abrem a nota, embora haja uma dezena de correções</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -7455,6 +10580,16 @@
           <t>https://github.com/coder/code-server/compare/v4.117.0...v4.118.0</t>
         </is>
       </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>única mudança é a atualização da base do Code (VS Code); sem correção própria nem recurso</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -7477,6 +10612,16 @@
           <t>https://github.com/coder/code-server/compare/v4.118.0...v4.121.0</t>
         </is>
       </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>única mudança é a atualização da base do Code (VS Code); sem correção própria nem recurso</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -7499,6 +10644,16 @@
           <t>https://github.com/coder/code-server/compare/v4.128.0...v4.129.0</t>
         </is>
       </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>única mudança é a atualização da base do Code (VS Code); sem correção própria nem recurso</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -7521,6 +10676,16 @@
           <t>https://github.com/coder/code-server/compare/v4.132.0...v4.133.0</t>
         </is>
       </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>única mudança é a atualização da base do Code (VS Code); sem correção própria nem recurso</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -7543,6 +10708,16 @@
           <t>https://github.com/coder/code-server/compare/v4.137.0...v4.138.0</t>
         </is>
       </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>além do bump do Code, traz correção própria: o proxy de portas preservava caminho, query e fragmento ao reescrever URLs</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -7565,6 +10740,16 @@
           <t>https://github.com/spring-projects/spring-boot/compare/v3.5.6...v3.4.11</t>
         </is>
       </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>nove correções, docs e atualizações de dependências; sem recurso</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -7587,6 +10772,16 @@
           <t>https://github.com/spring-projects/spring-boot/compare/v4.0.1...v3.5.10</t>
         </is>
       </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>sete correções, docs e dependências; sem recurso</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -7609,6 +10804,16 @@
           <t>https://github.com/spring-projects/spring-boot/compare/v3.5.11...v4.0.3</t>
         </is>
       </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>dez correções contra uma constante nova (JavaVersion.TWENTY_SIX)</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -7631,6 +10836,16 @@
           <t>https://github.com/spring-projects/spring-boot/compare/v4.0.5...v4.0.6</t>
         </is>
       </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>24 correções (segurança padrão, symlinks, Cassandra, Docker Compose); docs e dependências</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -7653,6 +10868,16 @@
           <t>https://github.com/spring-projects/spring-boot/compare/v3.5.14...v4.1.0</t>
         </is>
       </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>a nota do GitHub lista 33 correções e só dois itens de recurso; é uma versão minor, e as novidades ficam fora desta nota, então a confiança é baixa</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -7675,6 +10900,16 @@
           <t>https://github.com/ionic-team/ionic-framework/compare/v8.7.9...v8.7.10</t>
         </is>
       </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>nota só com Bug Fixes: temporização de anúncios de erro de validação para leitores de tela</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -7697,6 +10932,16 @@
           <t>https://github.com/ionic-team/ionic-framework/compare/v8.8.1...v8.8.2</t>
         </is>
       </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>nota só com Bug Fixes (genéricos no Angular, checkbox, foco do datetime)</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -7719,6 +10964,16 @@
           <t>https://github.com/ionic-team/ionic-framework/compare/v8.8.2...v8.8.3</t>
         </is>
       </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>nota só com Bug Fixes (rolagem do datetime no iOS, input-otp desabilitado)</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -7741,6 +10996,16 @@
           <t>https://github.com/ionic-team/ionic-framework/compare/v8.8.5...v8.8.6</t>
         </is>
       </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>nota só com Bug Fixes (action-sheet, datetime, segment)</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -7763,6 +11028,16 @@
           <t>https://github.com/ionic-team/ionic-framework/compare/v8.8.12...v8.8.13</t>
         </is>
       </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>nota só com Bug Fixes (button, datetime-button, datetime)</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -7785,6 +11060,16 @@
           <t>https://github.com/harry0703/MoneyPrinterTurbo/compare/v1.2.6...v1.2.7</t>
         </is>
       </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>seis correções (Edge TTS, legendas, uploads, montagem de vídeo, validação de caminhos) e migração para uv/README</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -7807,6 +11092,16 @@
           <t>https://github.com/harry0703/MoneyPrinterTurbo/compare/v1.2.8...v1.2.9</t>
         </is>
       </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>quatro recursos (controles de roteiro, MiMo LLM/TTS) ao lado de seis correções</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -7829,6 +11124,16 @@
           <t>https://github.com/harry0703/MoneyPrinterTurbo/compare/v1.3.1...v1.3.2</t>
         </is>
       </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>WebUI redesenhada, gerenciamento de tarefas, tour e CLI expandido</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -7851,6 +11156,16 @@
           <t>https://github.com/harry0703/MoneyPrinterTurbo/compare/v1.3.5...v1.3.6</t>
         </is>
       </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>novos provedores de vídeo/LLM e modos de recorte; correções são secundárias</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -7871,6 +11186,16 @@
       <c r="D301" s="2" t="inlineStr">
         <is>
           <t>https://github.com/harry0703/MoneyPrinterTurbo/compare/v1.3.6...v1.3.7</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>legendas palavra a palavra, música de fundo, provedores Kokoro/VoxCPM/Claude Code</t>
         </is>
       </c>
     </row>
